--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -540,12 +540,12 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>Main marketing landing page</t>
+          <t>Main marketing landing page. Redesign in progress on the redesign branch: full-bleed landscape hero, shared Footer component.</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I3" s="15" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I19" s="15" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Step, plan, testimonial, credibility, metric, case stat, case quote, speaker, form field, mobile menu link, author chip, author stack, post card, tag group, breadcrumb, author panel.</t>
+          <t>Step, plan, testimonial, credibility, metric, case stat, case quote, speaker, form field, mobile menu link, author chip, author stack, post card, tag group, breadcrumb, author panel. Hero media, footer columns.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="8" min="1" max="1"/>
@@ -540,12 +540,12 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>Main marketing landing page. Redesign in progress on the redesign branch: full-bleed landscape hero, shared Footer component.</t>
+          <t>Main marketing landing page, the live design. The Duna-idiom redesign moved to /v1 on 2026-09-07; this page and global.css are production and are not touched by variation work.</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="9">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Design System — Molecules</t>
@@ -1392,6 +1392,194 @@
       <c r="I20" s="15" t="inlineStr">
         <is>
           <t>Step, plan, testimonial, credibility, metric, case stat, case quote, speaker, form field, mobile menu link, author chip, author stack, post card, tag group, breadcrumb, author panel. Hero media, footer columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="9">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Design v1</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>https://compoundhealth.io/v1</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>/v1</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Noindex</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>V1Layout</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>src/pages/v1/index.astro</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Home page design variation v1, the Duna-idiom redesign moved off / on 2026-09-07. Own stylesheet src/styles/variants/v1.css. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="9">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Design v1.1</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>https://compoundhealth.io/v1-1</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>/v1-1</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Noindex</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>VariantStubLayout</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>src/pages/v1-1/index.astro</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Placeholder for an iteration on v1. Not designed yet; the route exists so the variation switcher works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="9">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Design v2</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>https://compoundhealth.io/v2</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>/v2</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Noindex</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>VariantStubLayout</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>src/pages/v2/index.astro</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>Placeholder for a second design direction. Not designed yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="9">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Design v3</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>https://compoundhealth.io/v3</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>/v3</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Noindex</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>VariantStubLayout</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>src/pages/v3/index.astro</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Placeholder for a third design direction. Not designed yet.</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="110" customWidth="1" style="8" min="1" max="1"/>
@@ -1569,6 +1757,13 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Design variations (/v1, /v1-1, /v2, /v3) are internal review routes: always Noindex, blocked in robots.txt, never in the sitemap. See CLAUDE.md, "Design variations".</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>Main marketing landing page, the live design. The Duna-idiom redesign moved to /v1 on 2026-09-07; this page and global.css are production and are not touched by variation work.</t>
+          <t>Main marketing landing page, the live design. The Duna-idiom redesign moved to /v1 on 2026-09-07; this page and global.css are production and are not touched by variation work. Carries the temporary variation switcher (src/components/variants/VariantSwitcher.astro) for review on the redesign branch; remove it before shipping.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Design variations (/v1, /v1-1, /v2, /v3) are internal review routes: always Noindex, blocked in robots.txt, never in the sitemap. See CLAUDE.md, "Design variations".</t>
         </is>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>VariantStubLayout</t>
+          <t>V11Layout</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Placeholder for an iteration on v1. Not designed yet; the route exists so the variation switcher works.</t>
+          <t>Home page design variation v1.1, forked from v1 on 2026-09-07 as an exact copy and iterated from there. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v1.1, forked from v1 on 2026-09-07 as an exact copy and iterated from there. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. The two 3D renders are pending; the hero and footer run as gradients until they land, see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>VariantStubLayout</t>
+          <t>V2Layout</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>Placeholder for a second design direction. Not designed yet.</t>
+          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark cocoa ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. The two 3D renders are pending; the hero and footer run as gradients until they land, see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. Hero art is the marble-tree render at public/images/v1-1/hero-monolith.webp; the footer render is still pending and that slot runs as a gradient, see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. Hero art is the marble-tree render at public/images/v1-1/hero-monolith.webp; the footer render is still pending and that slot runs as a gradient, see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. Both 3D renders are in, at public/images/v1-1/ (hero-monolith.webp, footer-stone.webp), see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>VariantStubLayout</t>
+          <t>V3Layout</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>Placeholder for a third design direction. Not designed yet.</t>
+          <t>Home page design variation v3, the lassie.ai idiom, built 2026-09-10. One cream ground with no bands and no shadows, Newsreader at 350 standing in for ABC Marist plus DM Sans and DM Mono, a floating glass nav pill, and scroll used as a mechanism: the hero window closes on itself, three panels deal like a deck on a pinned stage, and six tiles orbit a scroll-scrubbed ellipse around a line that changes under them. Own stylesheet src/styles/variants/v3.css and own layout V3Layout. Photography is placeholder-only; the seven slots and their prompts are in docs/v3-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1574,12 +1574,12 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v3, the lassie.ai idiom, built 2026-09-10. One cream ground with no bands and no shadows, Newsreader at 350 standing in for ABC Marist plus DM Sans and DM Mono, a floating glass nav pill, and scroll used as a mechanism: the hero window closes on itself, three panels deal like a deck on a pinned stage, and six tiles orbit a scroll-scrubbed ellipse around a line that changes under them. Own stylesheet src/styles/variants/v3.css and own layout V3Layout. Photography is placeholder-only; the seven slots and their prompts are in docs/v3-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v3, the lassie.ai idiom, built 2026-09-10. One cream ground with no bands and no shadows, Newsreader at 350 standing in for ABC Marist plus DM Sans and DM Mono, a floating glass nav pill, and scroll used as a mechanism: the hero window closes on itself, three panels deal like a deck on a pinned stage, and six tiles orbit a scroll-scrubbed ellipse around a line that changes under them. Own stylesheet src/styles/variants/v3.css and own layout V3Layout. All four photographs are in at public/images/v3/; the hero and the closing frame were graded so white type reads without a scrim, per docs/v3-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="8" min="1" max="1"/>
@@ -1445,17 +1445,17 @@
     <row r="22" s="9">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Design v1.1</t>
+          <t>Design v2</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>https://compoundhealth.io/v1-1</t>
+          <t>https://compoundhealth.io/v2</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>/v1-1</t>
+          <t>/v2</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>V11Layout</t>
+          <t>V2Layout</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>src/pages/v1-1/index.astro</t>
+          <t>src/pages/v2/index.astro</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
@@ -1485,24 +1485,24 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v1.1, forked from v1 on 2026-09-07. Answers the client feedback that v1 was not premium enough: bayshore.ai palette and gradient environments, square geometry, Cinzel Roman-caps labels, visible grid hairlines. Own stylesheet src/styles/variants/v1-1.css and own layout V11Layout. Both 3D renders are in, at public/images/v1-1/ (hero-monolith.webp, footer-stone.webp), see docs/v1-1-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark cocoa ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>
     <row r="23" s="9">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Design v2</t>
+          <t>Design v3</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>https://compoundhealth.io/v2</t>
+          <t>https://compoundhealth.io/v3</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>/v2</t>
+          <t>/v3</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
@@ -1517,72 +1517,26 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>V2Layout</t>
+          <t>V3Layout</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>src/pages/v2/index.astro</t>
+          <t>src/pages/v3/index.astro</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark cocoa ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" s="9">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Design v3</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>https://compoundhealth.io/v3</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>/v3</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Noindex</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>V3Layout</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>src/pages/v3/index.astro</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
           <t>Home page design variation v3, the lassie.ai idiom, built 2026-09-10. One cream ground with no bands and no shadows, Newsreader at 350 standing in for ABC Marist plus DM Sans and DM Mono, a floating glass nav pill, and scroll used as a mechanism: the hero window closes on itself, three panels deal like a deck on a pinned stage, and six tiles orbit a scroll-scrubbed ellipse around a line that changes under them. Own stylesheet src/styles/variants/v3.css and own layout V3Layout. All four photographs are in at public/images/v3/; the hero and the closing frame were graded so white type reads without a scrim, per docs/v3-art-brief.md. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>
+    <row r="24" s="9"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark cocoa ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. One palette, the brand green: the Dawn and Dusk themes and the theme switcher were removed on 2026-09-11 and Sage folded into :root as the only one. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. One palette, the brand green: the Dawn and Dusk themes and the theme switcher were removed on 2026-09-11 and Sage folded into :root as the only one. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v2, the joindawn.com idiom, built 2026-09-07. A dark ground the page opens on, a split hero of two rounded cards, one circle whose arc is drawn by scroll, a sunrise gradient into cream, then stacked sections with rounded feet, a coverflow carousel and a sky card. Source Serif 4 and Figtree. One palette, the brand green: the Dawn and Dusk themes and the theme switcher were removed on 2026-09-11 and Sage folded into :root as the only one. The logo is the 2026-09-11 lockup, drawn inline in V2Logo.astro and the mark alone under 480px; v1 and v3 keep the older Logo.astro. Own stylesheet src/styles/variants/v2.css and own layout V2Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>Home page design variation v1, the Duna-idiom redesign moved off / on 2026-09-07. Own stylesheet src/styles/variants/v1.css. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
+          <t>Home page design variation v1, the client's final version, delivered 2026-09-11 as one flattened page and revised the same day (client_resources/compound-health-v1-new.html), applied to the project that day. The revision broke the curated note onto two lines above 640px, suppressed that break below it, and removed the hairline rule between the curated and partners sections. superpower.com's type scale and zinc / vermillion palette with the client's brand tones (rust, umber, bronze, moss) carrying the accent, Aeonik at 400 and 500, one white ground, a transparent nav that collapses into a blurred pill on scroll, a photographic hero card with the credibility items along its foot, auto-rotating discipline tabs, and a fixed footer the closing card uncovers. Photographs at public/images/v1/, faces at public/fonts/. Own lockup in V1Logo.astro; own stylesheet src/styles/variants/v1.css and own layout V1Layout. noindex hard-coded in the layout, blocked in robots.txt, excluded from sitemap.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="8" min="1" max="1"/>
@@ -687,6 +687,53 @@
       <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Private advisor-facing partnership page. noindex=true; excluded from sitemap. Contains [TO CONFIRM] placeholders for commercial and compliance detail. The one page still on the previous design system, now at src/styles/legacy.css behind MainLayout: it was kept on 2026-09-14 because the new home page's bar and footer both link to it, and it has not been redesigned. Redesigning it retires legacy.css and MainLayout with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="9">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Not found (404)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>https://compoundhealth.io/404</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>/404</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Noindex</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>SiteLayout</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>src/pages/404.astro</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>The 404 page, added 2026-09-14. Hand-written on SiteLayout, so the port script neither writes nor overwrites it. noindex via the layout prop, which also suppresses the canonical; excluded from sitemap.xml. A static host serves it for an unknown path: confirm after deployment that it comes back with a real 404 status and not a 200, which is the failure it exists to prevent and cannot be tested from the repo.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Archived</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>MainLayout</t>
+          <t>MainLayout (not routed)</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>src/pages/for-advisors.astro</t>
+          <t>src/pages/_for-advisors.astro</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>Private advisor-facing partnership page. noindex=true; excluded from sitemap. Contains [TO CONFIRM] placeholders for commercial and compliance detail. The one page still on the previous design system, now at src/styles/legacy.css behind MainLayout: it was kept on 2026-09-14 because the new home page's bar and footer both link to it, and it has not been redesigned. Redesigning it retires legacy.css and MainLayout with it.</t>
+          <t>/for-advisors redirects to the home page as of 2026-09-14. The redirect is declared in astro.config.mjs; a static build emits dist/for-advisors/index.html as a meta-refresh document carrying noindex and a canonical at https://compoundhealth.io/, not a 301. The real 301 belongs at the host, with the www and trailing-slash decisions still open. The page source is kept at src/pages/_for-advisors.astro: the leading underscore takes it out of Astro routing, so the draft stays in the tree without answering a request and without colliding with the redirect. It is the private advisor-facing partnership page and still holds [TO CONFIRM] placeholders for commercial and compliance detail. Nothing routes MainLayout or src/styles/legacy.css any more, so neither is emitted into dist; both are kept for when the page is redesigned. The home page bar and footer still link to /for-advisors, so those links now bounce back to the home page: both are generated files and the fix belongs in scripts/port-drop.py or in the next client drop, not in a hand edit.</t>
         </is>
       </c>
     </row>

--- a/PAGES.xlsx
+++ b/PAGES.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>The live home page. The client's final design, delivered 2026-09-14 as one flattened self-contained file (client_resources/final_version/compound-health-v1.html) and ported by scripts/port-drop.py. This replaced the previous live home page and the /v1, /v2 and /v3 variations, which were deleted the same day. superpower.com's type scale and zinc palette with the client's brand tones (rust, umber, bronze, moss, sand) carrying the accent, Aeonik at 400 and 500, one white ground, a transparent bar that collapses into a blurred pill on scroll (aligned to the 1120px content column since this drop), a photographic hero card with the credibility items along its foot, auto-rotating discipline tabs, and a fixed footer the closing card uncovers. Photographs at public/images/, faces at public/fonts/.</t>
+          <t>The live home page. The client's final design, delivered 2026-09-14 as one flattened self-contained file (client_resources/final_version/compound-health-v1.html) and ported by scripts/port-drop.py. This replaced the previous live home page and the /v1, /v2 and /v3 variations, which were deleted the same day. A fluid type scale and a zinc palette, with the client's brand tones (rust, umber, bronze, moss, sand) carrying the accent, Aeonik at 400 and 500, one white ground, a transparent bar that collapses into a blurred pill on scroll (aligned to the 1120px content column since this drop), a photographic hero card with the credibility items along its foot, auto-rotating discipline tabs, and a fixed footer the closing card uncovers. Photographs at public/images/, faces at public/fonts/.</t>
         </is>
       </c>
     </row>
